--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uf-indicateur.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uf-indicateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uf-indicateur.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uf-indicateur.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf#Organization</t>
+    <t>element:Organization</t>
   </si>
   <si>
     <t>ID</t>
@@ -368,7 +368,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-uf-indicateur|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-uf-indicateur|2.2.0</t>
   </si>
 </sst>
 </file>
@@ -714,7 +714,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.40234375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.85546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
